--- a/survey_templates/038_management_audit_questionnaire--survey_templates.xlsx
+++ b/survey_templates/038_management_audit_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>current_position</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what_is_your_name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your current role/position in the company?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please specify your role/position.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>short_term_goals</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_your_organization</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What are your short-term goals?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please specify your short-term goals.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,64 +574,76 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>goals</t>
+          <t>long_term_goals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_are_your_goals</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What are your long-term goals?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please specify your long-term goals.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_4</t>
+          <t>how_goals_are_achieved</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_is_your_department</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How do you currently achieve your goals?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please specify how you currently achieve your goals.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_5</t>
+          <t>how_goals_are_planned</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_is_your_position</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How often do you plan to achieve your goals?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please specify how often you plan to achieve your goals.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +655,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_6</t>
+          <t>evaluation_methods</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_is_your_salary</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What are your current evaluation methods?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please specify your evaluation methods.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_7</t>
+          <t>agreement_statements</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_is_your_salary_range</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How much do you agree or disagree with the following statements?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select an option for each statement.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,84 +709,100 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_8</t>
+          <t>management_style</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_is_your_work_type</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is your current management style?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please specify your management style.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_9</t>
+          <t>monitoring_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_is_your_work_schedule</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>How often do you monitor your performance?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please specify how often you monitor your performance.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_10</t>
+          <t>goal_review</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>how_do_you_work</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>How often do you review and adjust your goals?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please specify how often you review and adjust your goals.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page_11</t>
+          <t>performance_comment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>what_are_your_goals</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What are your comments about your performance?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide your comments about your performance.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page_12</t>
+          <t>suggestion_for_improvement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>what_will_be_your_goals</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What are your suggestions for improvement?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide your suggestions for improvement.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,292 +844,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page_13</t>
+          <t>self_rating</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>when_will_goals_be_achieved</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>How do you rate your overall performance?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please rate your overall performance.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page_14</t>
+          <t>end_comments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>what_are_your_current_goals</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What are your comments?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide your comments.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>how_do_you_currently_achieve_goals</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>what_are_your_current_goals</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>what_do_you_currently_do</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>how_do_you_plan</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>how_do_you_maintain</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>how_do_you_monitor</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>what_is_your_evaluation</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>how_much_do_you_agree</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>what_is_your_reason</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>what_is_your_comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>what_is_your_comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +901,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,714 +929,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>how_goals_are_achieved_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>management</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>how_goals_are_achieved_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>consulting</t>
+          <t>sporadically</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Sporadically</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>how_goals_are_achieved_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>how_goals_are_planned_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>increase_productivity</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Increase productivity</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>how_goals_are_planned_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>improve_efficiency</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Improve efficiency</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>how_goals_are_planned_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>enhance_employee_engagement</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Enhance employee engagement</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>agreement_statements_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>agreement_statements_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>short-term</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Short-term</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>agreement_statements_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>long-term</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Long-term</t>
+          <t>Neither Agree nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>agreement_statements_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>agreement_statements_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>monitoring_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>monitoring_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>sporadically</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Sporadically</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>monitoring_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>short-term</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Short-term</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>goal_review_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>long-term</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Long-term</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>goal_review_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>sporadically</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Sporadically</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>page_15_choices</t>
+          <t>goal_review_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>regularly</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Regularly</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>page_15_choices</t>
+          <t>self_rating_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sporadically</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sporadically</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>page_15_choices</t>
+          <t>self_rating_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>page_16_choices</t>
+          <t>self_rating_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>short-term</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Short-term</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>page_16_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>long-term</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>page_16_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>page_17_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>manage</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Manage</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>page_17_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>plan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>page_17_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>monitor</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Monitor</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>page_18_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>regularly</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Regularly</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>page_18_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sporadically</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Sporadically</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>page_18_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>page_19_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>regularly</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Regularly</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>page_19_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>sporadically</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Sporadically</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>page_19_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>regularly</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Regularly</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>sporadically</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Sporadically</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
           <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>strongly_agree</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Strongly Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>somewhat_agree</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Somewhat Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>neither_agree_nor_disagree</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Neither Agree nor Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>somewhat_disagree</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Somewhat Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>strongly_disagree</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
